--- a/business_forms/035_credit_dispute_report_form--business_forms.xlsx
+++ b/business_forms/035_credit_dispute_report_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -765,8 +765,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -794,12 +794,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john_doe',_'selected':_false}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John Doe', 'selected': False}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane_doe',_'selected':_false}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane Doe', 'selected': False}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bob_smith',_'selected':_false}</t>
+          <t>bob_smith</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bob Smith', 'selected': False}</t>
+          <t>Bob Smith</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'credit_dispute'}</t>
+          <t>credit_dispute</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Credit Dispute'}</t>
+          <t>Credit Dispute</t>
         </is>
       </c>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'account_inaccuracy'}</t>
+          <t>account_inaccuracy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Account Inaccuracy'}</t>
+          <t>Account Inaccuracy</t>
         </is>
       </c>
     </row>
@@ -879,12 +879,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'identity_theft'}</t>
+          <t>identity_theft</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Identity Theft'}</t>
+          <t>Identity Theft</t>
         </is>
       </c>
     </row>
@@ -896,12 +896,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'disputed'}</t>
+          <t>disputed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Disputed'}</t>
+          <t>Disputed</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'resolved'}</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Resolved'}</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -930,12 +930,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -947,12 +947,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'submit_now'}</t>
+          <t>submit_now</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Submit Now'}</t>
+          <t>Submit Now</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'save_for_later'}</t>
+          <t>save_for_later</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Save for Later'}</t>
+          <t>Save for Later</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'submit_now'}</t>
+          <t>submit_now</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Submit Now'}</t>
+          <t>Submit Now</t>
         </is>
       </c>
     </row>
